--- a/WIP/Development Plans/活頁簿1.xlsx
+++ b/WIP/Development Plans/活頁簿1.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Emperors-and-Deities\WIP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Emperors-and-Deities\WIP\Development Plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF7D46B-1A98-4490-B120-B6D5B01D154C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CA377C-03D6-4281-A349-987AE0914076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" firstSheet="2" activeTab="3" xr2:uid="{C881A156-6EEB-4E61-80C2-9FE9DE8F1D18}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{C881A156-6EEB-4E61-80C2-9FE9DE8F1D18}"/>
   </bookViews>
   <sheets>
     <sheet name="Techtree" sheetId="5" r:id="rId1"/>
     <sheet name="PTechtree" sheetId="15" r:id="rId2"/>
     <sheet name="Promotion" sheetId="8" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="17" r:id="rId4"/>
-    <sheet name="Event" sheetId="16" r:id="rId5"/>
-    <sheet name="BuildingOLD" sheetId="11" r:id="rId6"/>
-    <sheet name="UnitsOLD" sheetId="9" r:id="rId7"/>
-    <sheet name="Civ DesignOLD(Out of Policy)" sheetId="6" r:id="rId8"/>
-    <sheet name="Civ DesignOLD(in Policy) chi" sheetId="13" r:id="rId9"/>
+    <sheet name="Tutorial Design" sheetId="17" r:id="rId4"/>
+    <sheet name="Resource Tree" sheetId="18" r:id="rId5"/>
+    <sheet name="Event" sheetId="16" r:id="rId6"/>
+    <sheet name="BuildingOLD" sheetId="11" r:id="rId7"/>
+    <sheet name="UnitsOLD" sheetId="9" r:id="rId8"/>
+    <sheet name="Civ DesignOLD(Out of Policy)" sheetId="6" r:id="rId9"/>
+    <sheet name="Civ DesignOLD(in Policy) chi" sheetId="13" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="821">
   <si>
     <t>Mining</t>
   </si>
@@ -3297,12 +3298,15 @@
     <t>Sidequests</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>2050ad-2075ad</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3696,12 +3700,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3710,6 +3708,12 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4250,60 +4254,66 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925E982B-F2BD-4380-9554-C8769344FDC4}">
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultColWidth="19" defaultRowHeight="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19" defaultRowHeight="38.4" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:35" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:35" ht="38.4" customHeight="1">
+      <c r="A1" s="52" t="s">
         <v>736</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52" t="s">
         <v>623</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49" t="s">
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52" t="s">
         <v>624</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49" t="s">
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52" t="s">
         <v>722</v>
       </c>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49" t="s">
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52" t="s">
         <v>721</v>
       </c>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49" t="s">
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52" t="s">
         <v>723</v>
       </c>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49" t="s">
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52" t="s">
         <v>725</v>
       </c>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49" t="s">
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52" t="s">
         <v>742</v>
       </c>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49" t="s">
+      <c r="X1" s="52"/>
+      <c r="Y1" s="52"/>
+      <c r="Z1" s="52"/>
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="52" t="s">
         <v>728</v>
       </c>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-    </row>
-    <row r="2" spans="1:35" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC1" s="52"/>
+      <c r="AD1" s="52"/>
+      <c r="AE1" s="52"/>
+      <c r="AF1" s="52" t="s">
+        <v>820</v>
+      </c>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+    </row>
+    <row r="2" spans="1:35" ht="38.4" customHeight="1">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4410,7 +4420,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="38.4" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
         <v>75</v>
@@ -4472,7 +4482,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="38.4" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>769</v>
       </c>
@@ -4534,7 +4544,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="38.4" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>155</v>
       </c>
@@ -4602,7 +4612,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="38.4" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>770</v>
       </c>
@@ -4655,7 +4665,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="38.4" customHeight="1">
       <c r="B8" s="2" t="s">
         <v>76</v>
       </c>
@@ -4705,7 +4715,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="38.4" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>771</v>
       </c>
@@ -4767,7 +4777,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="38.4" customHeight="1">
       <c r="B10" s="2" t="s">
         <v>78</v>
       </c>
@@ -4817,7 +4827,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="38.4" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="2" t="s">
         <v>79</v>
@@ -4875,7 +4885,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="AF1:AI1"/>
     <mergeCell ref="AB1:AE1"/>
     <mergeCell ref="S1:V1"/>
     <mergeCell ref="A1:B1"/>
@@ -4895,20 +4906,430 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B65134C7-4BA5-4FC1-A5F8-F4E5303A0F6D}">
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultColWidth="22" defaultRowHeight="68.25" customHeight="1"/>
+  <cols>
+    <col min="3" max="3" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="68.25" customHeight="1">
+      <c r="B1" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D2" t="s">
+        <v>620</v>
+      </c>
+      <c r="F2" t="s">
+        <v>616</v>
+      </c>
+      <c r="H2" t="s">
+        <v>621</v>
+      </c>
+      <c r="J2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A3" t="s">
+        <v>582</v>
+      </c>
+      <c r="B3" t="s">
+        <v>539</v>
+      </c>
+      <c r="D3" t="s">
+        <v>608</v>
+      </c>
+      <c r="F3" t="s">
+        <v>607</v>
+      </c>
+      <c r="H3" t="s">
+        <v>619</v>
+      </c>
+      <c r="J3" t="s">
+        <v>570</v>
+      </c>
+      <c r="M3" t="s">
+        <v>538</v>
+      </c>
+      <c r="N3" t="s">
+        <v>527</v>
+      </c>
+      <c r="P3" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B4" t="s">
+        <v>776</v>
+      </c>
+      <c r="D4" t="s">
+        <v>605</v>
+      </c>
+      <c r="F4" t="s">
+        <v>560</v>
+      </c>
+      <c r="H4" t="s">
+        <v>604</v>
+      </c>
+      <c r="J4" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B5" t="s">
+        <v>540</v>
+      </c>
+      <c r="D5" t="s">
+        <v>547</v>
+      </c>
+      <c r="F5" t="s">
+        <v>558</v>
+      </c>
+      <c r="H5" t="s">
+        <v>561</v>
+      </c>
+      <c r="J5" t="s">
+        <v>571</v>
+      </c>
+      <c r="P5" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A6" t="s">
+        <v>585</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>540</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>548</v>
+      </c>
+      <c r="F6" s="52" t="s">
+        <v>773</v>
+      </c>
+      <c r="H6" t="s">
+        <v>775</v>
+      </c>
+      <c r="J6" t="s">
+        <v>554</v>
+      </c>
+      <c r="P6" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A7" t="s">
+        <v>586</v>
+      </c>
+      <c r="B7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="H7" t="s">
+        <v>774</v>
+      </c>
+      <c r="J7" t="s">
+        <v>572</v>
+      </c>
+      <c r="P7" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A8" t="s">
+        <v>587</v>
+      </c>
+      <c r="B8" t="s">
+        <v>575</v>
+      </c>
+      <c r="D8" t="s">
+        <v>580</v>
+      </c>
+      <c r="F8" t="s">
+        <v>609</v>
+      </c>
+      <c r="H8" t="s">
+        <v>609</v>
+      </c>
+      <c r="J8" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A9" t="s">
+        <v>588</v>
+      </c>
+      <c r="B9" t="s">
+        <v>541</v>
+      </c>
+      <c r="D9" t="s">
+        <v>610</v>
+      </c>
+      <c r="F9" t="s">
+        <v>573</v>
+      </c>
+      <c r="H9" t="s">
+        <v>562</v>
+      </c>
+      <c r="J9" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A10" t="s">
+        <v>589</v>
+      </c>
+      <c r="B10" t="s">
+        <v>611</v>
+      </c>
+      <c r="D10" t="s">
+        <v>549</v>
+      </c>
+      <c r="F10" t="s">
+        <v>559</v>
+      </c>
+      <c r="H10" t="s">
+        <v>563</v>
+      </c>
+      <c r="J10" t="s">
+        <v>559</v>
+      </c>
+      <c r="P10" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A11" t="s">
+        <v>590</v>
+      </c>
+      <c r="B11" t="s">
+        <v>542</v>
+      </c>
+      <c r="D11" t="s">
+        <v>550</v>
+      </c>
+      <c r="F11" t="s">
+        <v>555</v>
+      </c>
+      <c r="H11" t="s">
+        <v>564</v>
+      </c>
+      <c r="J11" t="s">
+        <v>603</v>
+      </c>
+      <c r="P11" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B12" t="s">
+        <v>613</v>
+      </c>
+      <c r="D12" t="s">
+        <v>551</v>
+      </c>
+      <c r="F12" t="s">
+        <v>615</v>
+      </c>
+      <c r="H12" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A13" t="s">
+        <v>592</v>
+      </c>
+      <c r="B13" t="s">
+        <v>614</v>
+      </c>
+      <c r="D13" t="s">
+        <v>600</v>
+      </c>
+      <c r="F13" t="s">
+        <v>601</v>
+      </c>
+      <c r="H13" t="s">
+        <v>599</v>
+      </c>
+      <c r="J13" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A14" t="s">
+        <v>593</v>
+      </c>
+      <c r="B14" t="s">
+        <v>543</v>
+      </c>
+      <c r="D14" t="s">
+        <v>552</v>
+      </c>
+      <c r="H14" t="s">
+        <v>565</v>
+      </c>
+      <c r="P14" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A15" t="s">
+        <v>594</v>
+      </c>
+      <c r="B15" t="s">
+        <v>546</v>
+      </c>
+      <c r="H15" t="s">
+        <v>567</v>
+      </c>
+      <c r="J15" t="s">
+        <v>581</v>
+      </c>
+      <c r="P15" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A16" t="s">
+        <v>595</v>
+      </c>
+      <c r="B16" t="s">
+        <v>545</v>
+      </c>
+      <c r="F16" t="s">
+        <v>556</v>
+      </c>
+      <c r="H16" t="s">
+        <v>566</v>
+      </c>
+      <c r="P16" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A17" t="s">
+        <v>596</v>
+      </c>
+      <c r="B17" t="s">
+        <v>544</v>
+      </c>
+      <c r="D17" t="s">
+        <v>553</v>
+      </c>
+      <c r="F17" t="s">
+        <v>556</v>
+      </c>
+      <c r="H17" t="s">
+        <v>568</v>
+      </c>
+      <c r="P17" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A18" t="s">
+        <v>597</v>
+      </c>
+      <c r="B18" t="s">
+        <v>576</v>
+      </c>
+      <c r="D18" t="s">
+        <v>578</v>
+      </c>
+      <c r="F18" t="s">
+        <v>557</v>
+      </c>
+      <c r="H18" t="s">
+        <v>569</v>
+      </c>
+      <c r="J18" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="68.25" customHeight="1">
+      <c r="A19" t="s">
+        <v>598</v>
+      </c>
+      <c r="B19" t="s">
+        <v>577</v>
+      </c>
+      <c r="D19" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="68.25" customHeight="1">
+      <c r="P20" s="11" t="s">
+        <v>528</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="B6:B7"/>
+  </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{581CEC18-D5B4-4F4B-9A42-44E7072E5DD5}">
   <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultColWidth="19.375" defaultRowHeight="39" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="19.36328125" defaultRowHeight="39" customHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="19.375" style="13"/>
+    <col min="1" max="16384" width="19.36328125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="50" t="s">
+    <row r="1" spans="1:13" ht="39" customHeight="1">
+      <c r="B1" s="53" t="s">
         <v>719</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
       <c r="E1" s="29" t="s">
         <v>98</v>
       </c>
@@ -4934,7 +5355,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="39" customHeight="1">
       <c r="A2" s="26"/>
       <c r="B2" s="14" t="s">
         <v>707</v>
@@ -4967,7 +5388,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="39" customHeight="1">
       <c r="J3" s="15" t="s">
         <v>704</v>
       </c>
@@ -4979,7 +5400,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="39" customHeight="1">
       <c r="B4" s="25" t="s">
         <v>701</v>
       </c>
@@ -5001,7 +5422,7 @@
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
     </row>
-    <row r="5" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="39" customHeight="1">
       <c r="B5" s="24" t="s">
         <v>694</v>
       </c>
@@ -5030,7 +5451,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="39" customHeight="1">
       <c r="D6" s="23" t="s">
         <v>686</v>
       </c>
@@ -5055,7 +5476,7 @@
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="39" customHeight="1">
       <c r="B7" s="23" t="s">
         <v>680</v>
       </c>
@@ -5084,7 +5505,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="39" customHeight="1">
       <c r="E8" s="23" t="s">
         <v>678</v>
       </c>
@@ -5102,7 +5523,7 @@
       </c>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="39" customHeight="1">
       <c r="C9" s="21" t="s">
         <v>666</v>
       </c>
@@ -5134,7 +5555,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="39" customHeight="1">
       <c r="C10" s="21" t="s">
         <v>658</v>
       </c>
@@ -5159,7 +5580,7 @@
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="39" customHeight="1">
       <c r="B11" s="20" t="s">
         <v>651</v>
       </c>
@@ -5185,7 +5606,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="39" customHeight="1">
       <c r="B12" s="17" t="s">
         <v>643</v>
       </c>
@@ -5207,7 +5628,7 @@
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="39" customHeight="1">
       <c r="B13" s="17" t="s">
         <v>637</v>
       </c>
@@ -5227,7 +5648,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="39" customHeight="1">
       <c r="B14" s="15"/>
       <c r="E14" s="15"/>
       <c r="G14" s="15"/>
@@ -5240,7 +5661,7 @@
       </c>
       <c r="M14" s="15"/>
     </row>
-    <row r="15" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="39" customHeight="1">
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -5256,7 +5677,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="39" customHeight="1">
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
@@ -5273,7 +5694,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:10" ht="39" customHeight="1">
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
@@ -5284,7 +5705,7 @@
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
     </row>
-    <row r="18" spans="2:10" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:10" ht="39" customHeight="1">
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -5307,12 +5728,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B53FB35-CF66-4CF1-8CCA-C87A13BE0A97}">
   <dimension ref="A1:H57"/>
-  <sheetFormatPr defaultColWidth="16.25" defaultRowHeight="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="16.26953125" defaultRowHeight="32.4" customHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="16.25" style="40"/>
+    <col min="1" max="16384" width="16.26953125" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="32.4" customHeight="1">
       <c r="A1" s="40" t="s">
         <v>253</v>
       </c>
@@ -5332,7 +5753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="32.4" customHeight="1">
       <c r="A2" s="40" t="s">
         <v>255</v>
       </c>
@@ -5343,7 +5764,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="32.4" customHeight="1">
       <c r="A3" s="42">
         <v>2</v>
       </c>
@@ -5354,7 +5775,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="32.4" customHeight="1">
       <c r="A4" s="42">
         <v>3</v>
       </c>
@@ -5365,22 +5786,22 @@
         <v>216</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="32.4" customHeight="1">
       <c r="B5" s="40" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="32.4" customHeight="1">
       <c r="B6" s="40" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="32.4" customHeight="1">
       <c r="B7" s="41" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="32.4" customHeight="1">
       <c r="A8" s="40" t="s">
         <v>163</v>
       </c>
@@ -5400,7 +5821,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="32.4" customHeight="1">
       <c r="B9" s="40" t="s">
         <v>787</v>
       </c>
@@ -5414,7 +5835,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="32.4" customHeight="1">
       <c r="B10" s="40" t="s">
         <v>246</v>
       </c>
@@ -5428,7 +5849,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="32.4" customHeight="1">
       <c r="B11" s="40" t="s">
         <v>245</v>
       </c>
@@ -5442,7 +5863,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="32.4" customHeight="1">
       <c r="B12" s="40" t="s">
         <v>247</v>
       </c>
@@ -5456,7 +5877,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="32.4" customHeight="1">
       <c r="B13" s="40" t="s">
         <v>788</v>
       </c>
@@ -5470,7 +5891,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="32.4" customHeight="1">
       <c r="B14" s="40" t="s">
         <v>790</v>
       </c>
@@ -5484,7 +5905,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="32.4" customHeight="1">
       <c r="B15" s="40" t="s">
         <v>789</v>
       </c>
@@ -5498,7 +5919,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="32.4" customHeight="1">
       <c r="B16" s="40" t="s">
         <v>791</v>
       </c>
@@ -5512,7 +5933,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="32.4" customHeight="1">
       <c r="B17" s="40" t="s">
         <v>792</v>
       </c>
@@ -5526,7 +5947,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="32.4" customHeight="1">
       <c r="B18" s="40" t="s">
         <v>793</v>
       </c>
@@ -5540,7 +5961,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="32.4" customHeight="1">
       <c r="B19" s="40" t="s">
         <v>794</v>
       </c>
@@ -5554,7 +5975,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="32.4" customHeight="1">
       <c r="A20" s="40" t="s">
         <v>779</v>
       </c>
@@ -5577,7 +5998,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="32.4" customHeight="1">
       <c r="A24" s="40" t="s">
         <v>332</v>
       </c>
@@ -5591,7 +6012,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="32.4" customHeight="1">
       <c r="B25" s="40" t="s">
         <v>215</v>
       </c>
@@ -5599,7 +6020,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="32.4" customHeight="1">
       <c r="A26" s="40" t="s">
         <v>333</v>
       </c>
@@ -5616,7 +6037,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="32.4" customHeight="1">
       <c r="B27" s="40" t="s">
         <v>192</v>
       </c>
@@ -5630,7 +6051,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="32.4" customHeight="1">
       <c r="B28" s="44" t="s">
         <v>198</v>
       </c>
@@ -5638,7 +6059,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="32.4" customHeight="1">
       <c r="A29" s="40" t="s">
         <v>334</v>
       </c>
@@ -5650,7 +6071,7 @@
       </c>
       <c r="G29" s="43"/>
     </row>
-    <row r="30" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="32.4" customHeight="1">
       <c r="B30" s="40" t="s">
         <v>188</v>
       </c>
@@ -5667,7 +6088,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="32.4" customHeight="1">
       <c r="B31" s="43" t="s">
         <v>206</v>
       </c>
@@ -5675,7 +6096,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="32.4" customHeight="1">
       <c r="B32" s="40" t="s">
         <v>193</v>
       </c>
@@ -5689,7 +6110,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="32.4" customHeight="1">
       <c r="A33" s="40" t="s">
         <v>335</v>
       </c>
@@ -5715,7 +6136,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="32.4" customHeight="1">
       <c r="A34" s="40" t="s">
         <v>336</v>
       </c>
@@ -5735,7 +6156,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="32.4" customHeight="1">
       <c r="B35" s="40" t="s">
         <v>194</v>
       </c>
@@ -5746,7 +6167,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="32.4" customHeight="1">
       <c r="A36" s="40" t="s">
         <v>337</v>
       </c>
@@ -5763,7 +6184,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="32.4" customHeight="1">
       <c r="B37" s="40" t="s">
         <v>200</v>
       </c>
@@ -5780,7 +6201,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="32.4" customHeight="1">
       <c r="B38" s="47" t="s">
         <v>214</v>
       </c>
@@ -5788,7 +6209,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="32.4" customHeight="1">
       <c r="B39" s="47" t="s">
         <v>258</v>
       </c>
@@ -5802,7 +6223,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="32.4" customHeight="1">
       <c r="A40" s="40" t="s">
         <v>338</v>
       </c>
@@ -5822,7 +6243,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="32.4" customHeight="1">
       <c r="B41" s="40" t="s">
         <v>251</v>
       </c>
@@ -5830,7 +6251,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="32.4" customHeight="1">
       <c r="A42" s="40" t="s">
         <v>339</v>
       </c>
@@ -5850,7 +6271,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="32.4" customHeight="1">
       <c r="A43" s="40" t="s">
         <v>767</v>
       </c>
@@ -5861,57 +6282,57 @@
         <v>768</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="32.4" customHeight="1">
       <c r="A46" s="40" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="32.4" customHeight="1">
       <c r="A47" s="40" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="32.4" customHeight="1">
       <c r="A48" s="40" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" ht="32.4" customHeight="1">
       <c r="A50" s="40" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" ht="32.4" customHeight="1">
       <c r="A51" s="40" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" ht="32.4" customHeight="1">
       <c r="A52" s="40" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" ht="32.4" customHeight="1">
       <c r="A53" s="40" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" ht="32.4" customHeight="1">
       <c r="A54" s="40" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" ht="32.4" customHeight="1">
       <c r="A55" s="40" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" ht="32.4" customHeight="1">
       <c r="A56" s="40" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" ht="32.4" customHeight="1">
       <c r="A57" s="40" t="s">
         <v>239</v>
       </c>
@@ -5926,92 +6347,92 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11D303E-D867-461B-840C-08DCC82C77DC}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="23" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23" defaultRowHeight="67.5" customHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="23" style="51"/>
+    <col min="1" max="16384" width="23" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+    <row r="1" spans="1:8" ht="67.5" customHeight="1">
+      <c r="A1" s="50" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53"/>
-    </row>
-    <row r="3" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+    <row r="2" spans="1:8" ht="67.5" customHeight="1">
+      <c r="A2" s="51"/>
+    </row>
+    <row r="3" spans="1:8" ht="67.5" customHeight="1">
+      <c r="A3" s="50" t="s">
         <v>809</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="49" t="s">
         <v>811</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="49" t="s">
         <v>812</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="49" t="s">
         <v>813</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="49" t="s">
         <v>818</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="49" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="53"/>
-    </row>
-    <row r="5" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53"/>
-      <c r="G5" s="51" t="s">
+    <row r="4" spans="1:8" ht="67.5" customHeight="1">
+      <c r="A4" s="51"/>
+    </row>
+    <row r="5" spans="1:8" ht="67.5" customHeight="1">
+      <c r="A5" s="51"/>
+      <c r="G5" s="49" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+    <row r="6" spans="1:8" ht="67.5" customHeight="1">
+      <c r="A6" s="51" t="s">
         <v>816</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="49" t="s">
         <v>814</v>
       </c>
-      <c r="G6" s="51" t="s">
+      <c r="G6" s="49" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+    <row r="7" spans="1:8" ht="67.5" customHeight="1">
+      <c r="A7" s="50" t="s">
         <v>810</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="49" t="s">
         <v>811</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="49" t="s">
         <v>812</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="49" t="s">
         <v>813</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="49" t="s">
         <v>818</v>
       </c>
-      <c r="G7" s="51" t="s">
+      <c r="G7" s="49" t="s">
         <v>819</v>
       </c>
-      <c r="H7" s="51" t="s">
+      <c r="H7" s="49" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="51" t="s">
+    <row r="8" spans="1:8" ht="67.5" customHeight="1">
+      <c r="E8" s="49" t="s">
         <v>815</v>
       </c>
-      <c r="G8" s="51" t="s">
+      <c r="G8" s="49" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G9" s="51" t="s">
+    <row r="9" spans="1:8" ht="67.5" customHeight="1">
+      <c r="G9" s="49" t="s">
         <v>819</v>
       </c>
     </row>
@@ -6023,11 +6444,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F27603-452E-4368-8825-D40650F48077}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="18.26953125" defaultRowHeight="35.4" customHeight="1"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9EFEAA4-1654-490A-AB7D-56B611AFF5FD}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="45" defaultRowHeight="47.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="45" defaultRowHeight="47.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="47.25" customHeight="1">
       <c r="A1" t="s">
         <v>797</v>
       </c>
@@ -6041,7 +6471,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="47.25" customHeight="1">
       <c r="A2" t="s">
         <v>801</v>
       </c>
@@ -6052,22 +6482,22 @@
         <v>807</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="47.25" customHeight="1">
       <c r="A3" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="47.25" customHeight="1">
       <c r="A4" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="47.25" customHeight="1">
       <c r="A5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="47.25" customHeight="1">
       <c r="A6" t="s">
         <v>805</v>
       </c>
@@ -6078,12 +6508,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F092E08-D523-4072-921C-A893C302A87B}">
   <dimension ref="A1:W12"/>
-  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="81.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="81.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:23" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="81.75" customHeight="1">
       <c r="A1" s="36">
         <v>0</v>
       </c>
@@ -6154,7 +6584,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="81.75" customHeight="1">
       <c r="A2" s="38" t="s">
         <v>374</v>
       </c>
@@ -6203,7 +6633,7 @@
       </c>
       <c r="W2" s="36"/>
     </row>
-    <row r="3" spans="1:23" ht="143.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" ht="143.25" customHeight="1">
       <c r="A3" s="37" t="s">
         <v>366</v>
       </c>
@@ -6254,7 +6684,7 @@
       <c r="V3" s="36"/>
       <c r="W3" s="36"/>
     </row>
-    <row r="4" spans="1:23" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="81.75" customHeight="1">
       <c r="A4" s="36"/>
       <c r="B4" s="38" t="s">
         <v>375</v>
@@ -6299,7 +6729,7 @@
       </c>
       <c r="W4" s="36"/>
     </row>
-    <row r="5" spans="1:23" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="81.75" customHeight="1">
       <c r="A5" s="36"/>
       <c r="B5" s="36"/>
       <c r="C5" s="37" t="s">
@@ -6344,7 +6774,7 @@
       <c r="V5" s="36"/>
       <c r="W5" s="36"/>
     </row>
-    <row r="6" spans="1:23" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="81.75" customHeight="1">
       <c r="A6" s="37" t="s">
         <v>397</v>
       </c>
@@ -6383,7 +6813,7 @@
       <c r="V6" s="36"/>
       <c r="W6" s="36"/>
     </row>
-    <row r="7" spans="1:23" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="81.75" customHeight="1">
       <c r="A7" s="37" t="s">
         <v>405</v>
       </c>
@@ -6424,7 +6854,7 @@
       <c r="V7" s="36"/>
       <c r="W7" s="36"/>
     </row>
-    <row r="8" spans="1:23" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" ht="81.75" customHeight="1">
       <c r="A8" s="36"/>
       <c r="B8" s="38" t="s">
         <v>412</v>
@@ -6455,7 +6885,7 @@
       <c r="V8" s="36"/>
       <c r="W8" s="36"/>
     </row>
-    <row r="9" spans="1:23" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="81.75" customHeight="1">
       <c r="A9" s="36"/>
       <c r="B9" s="36"/>
       <c r="C9" s="36"/>
@@ -6496,7 +6926,7 @@
       <c r="V9" s="36"/>
       <c r="W9" s="36"/>
     </row>
-    <row r="10" spans="1:23" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="81.75" customHeight="1">
       <c r="A10" s="36"/>
       <c r="B10" s="36"/>
       <c r="C10" s="37" t="s">
@@ -6537,7 +6967,7 @@
       <c r="V10" s="36"/>
       <c r="W10" s="36"/>
     </row>
-    <row r="11" spans="1:23" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="81.75" customHeight="1">
       <c r="A11" s="36"/>
       <c r="B11" s="37" t="s">
         <v>429</v>
@@ -6590,7 +7020,7 @@
       <c r="V11" s="36"/>
       <c r="W11" s="36"/>
     </row>
-    <row r="12" spans="1:23" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="81.75" customHeight="1">
       <c r="A12" s="36"/>
       <c r="B12" s="36"/>
       <c r="C12" s="38" t="s">
@@ -6640,12 +7070,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1F8F12-7BF1-4F36-BA5D-5C77B151C0AF}">
   <dimension ref="A1:AS18"/>
-  <sheetFormatPr defaultColWidth="17.375" defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="17.36328125" defaultRowHeight="24.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" ht="24.75" customHeight="1">
       <c r="A1" s="36"/>
       <c r="B1" s="35" t="s">
         <v>153</v>
@@ -6780,7 +7210,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" ht="24.75" customHeight="1">
       <c r="A2" s="36" t="s">
         <v>461</v>
       </c>
@@ -6835,7 +7265,7 @@
       <c r="AR2" s="36"/>
       <c r="AS2" s="36"/>
     </row>
-    <row r="3" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:45" ht="24.75" customHeight="1">
       <c r="A3" s="36" t="s">
         <v>460</v>
       </c>
@@ -6888,7 +7318,7 @@
       <c r="AR3" s="36"/>
       <c r="AS3" s="36"/>
     </row>
-    <row r="4" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" ht="24.75" customHeight="1">
       <c r="A4" s="36" t="s">
         <v>459</v>
       </c>
@@ -6949,7 +7379,7 @@
       <c r="AR4" s="36"/>
       <c r="AS4" s="36"/>
     </row>
-    <row r="5" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" ht="24.75" customHeight="1">
       <c r="A5" s="36" t="s">
         <v>462</v>
       </c>
@@ -7008,7 +7438,7 @@
       <c r="AR5" s="36"/>
       <c r="AS5" s="36"/>
     </row>
-    <row r="6" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" ht="24.75" customHeight="1">
       <c r="A6" s="36" t="s">
         <v>463</v>
       </c>
@@ -7077,7 +7507,7 @@
       <c r="AR6" s="36"/>
       <c r="AS6" s="36"/>
     </row>
-    <row r="7" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" ht="24.75" customHeight="1">
       <c r="A7" s="36" t="s">
         <v>464</v>
       </c>
@@ -7138,7 +7568,7 @@
       <c r="AR7" s="36"/>
       <c r="AS7" s="36"/>
     </row>
-    <row r="8" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" ht="24.75" customHeight="1">
       <c r="A8" s="36" t="s">
         <v>465</v>
       </c>
@@ -7207,7 +7637,7 @@
       <c r="AR8" s="36"/>
       <c r="AS8" s="36"/>
     </row>
-    <row r="9" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" ht="24.75" customHeight="1">
       <c r="A9" s="36" t="s">
         <v>466</v>
       </c>
@@ -7268,7 +7698,7 @@
       <c r="AR9" s="36"/>
       <c r="AS9" s="36"/>
     </row>
-    <row r="10" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" ht="24.75" customHeight="1">
       <c r="A10" s="36" t="s">
         <v>467</v>
       </c>
@@ -7333,7 +7763,7 @@
       <c r="AR10" s="36"/>
       <c r="AS10" s="36"/>
     </row>
-    <row r="11" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" ht="24.75" customHeight="1">
       <c r="A11" s="36" t="s">
         <v>468</v>
       </c>
@@ -7402,7 +7832,7 @@
       </c>
       <c r="AS11" s="36"/>
     </row>
-    <row r="12" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" ht="24.75" customHeight="1">
       <c r="A12" s="36" t="s">
         <v>469</v>
       </c>
@@ -7471,7 +7901,7 @@
       </c>
       <c r="AS12" s="36"/>
     </row>
-    <row r="13" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" ht="24.75" customHeight="1">
       <c r="A13" s="36"/>
       <c r="B13" s="36"/>
       <c r="C13" s="36"/>
@@ -7528,7 +7958,7 @@
       <c r="AR13" s="36"/>
       <c r="AS13" s="36"/>
     </row>
-    <row r="14" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" ht="24.75" customHeight="1">
       <c r="A14" s="36"/>
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
@@ -7579,7 +8009,7 @@
       <c r="AR14" s="36"/>
       <c r="AS14" s="36"/>
     </row>
-    <row r="15" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" ht="24.75" customHeight="1">
       <c r="A15" s="36"/>
       <c r="B15" s="36"/>
       <c r="C15" s="36"/>
@@ -7628,7 +8058,7 @@
       <c r="AR15" s="36"/>
       <c r="AS15" s="36"/>
     </row>
-    <row r="16" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" ht="24.75" customHeight="1">
       <c r="A16" s="36" t="s">
         <v>319</v>
       </c>
@@ -7685,7 +8115,7 @@
       <c r="AR16" s="36"/>
       <c r="AS16" s="36"/>
     </row>
-    <row r="17" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:45" ht="24.75" customHeight="1">
       <c r="A17" s="36" t="s">
         <v>330</v>
       </c>
@@ -7738,7 +8168,7 @@
       <c r="AR17" s="36"/>
       <c r="AS17" s="36"/>
     </row>
-    <row r="18" spans="1:45" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:45" ht="24.75" customHeight="1">
       <c r="A18" s="36" t="s">
         <v>495</v>
       </c>
@@ -7834,12 +8264,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBFFA452-D8B2-444A-A04B-53CFD30C9CB5}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="25.625" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="25.6328125" defaultRowHeight="21" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="21" customHeight="1">
       <c r="B1" s="6" t="s">
         <v>14</v>
       </c>
@@ -7868,7 +8298,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="21" customHeight="1">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7888,7 +8318,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="21" customHeight="1">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7905,7 +8335,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="21" customHeight="1">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7930,7 +8360,7 @@
       </c>
       <c r="J4" s="10"/>
     </row>
-    <row r="5" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="21" customHeight="1">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -7949,7 +8379,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -7976,7 +8406,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -7988,7 +8418,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -8008,7 +8438,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -8040,7 +8470,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -8054,7 +8484,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="C11" s="5"/>
       <c r="D11" s="6"/>
     </row>
@@ -8062,414 +8492,4 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B65134C7-4BA5-4FC1-A5F8-F4E5303A0F6D}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultColWidth="22" defaultRowHeight="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="5" t="s">
-        <v>531</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>606</v>
-      </c>
-      <c r="B2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D2" t="s">
-        <v>620</v>
-      </c>
-      <c r="F2" t="s">
-        <v>616</v>
-      </c>
-      <c r="H2" t="s">
-        <v>621</v>
-      </c>
-      <c r="J2" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>582</v>
-      </c>
-      <c r="B3" t="s">
-        <v>539</v>
-      </c>
-      <c r="D3" t="s">
-        <v>608</v>
-      </c>
-      <c r="F3" t="s">
-        <v>607</v>
-      </c>
-      <c r="H3" t="s">
-        <v>619</v>
-      </c>
-      <c r="J3" t="s">
-        <v>570</v>
-      </c>
-      <c r="M3" t="s">
-        <v>538</v>
-      </c>
-      <c r="N3" t="s">
-        <v>527</v>
-      </c>
-      <c r="P3" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>583</v>
-      </c>
-      <c r="B4" t="s">
-        <v>776</v>
-      </c>
-      <c r="D4" t="s">
-        <v>605</v>
-      </c>
-      <c r="F4" t="s">
-        <v>560</v>
-      </c>
-      <c r="H4" t="s">
-        <v>604</v>
-      </c>
-      <c r="J4" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>584</v>
-      </c>
-      <c r="B5" t="s">
-        <v>540</v>
-      </c>
-      <c r="D5" t="s">
-        <v>547</v>
-      </c>
-      <c r="F5" t="s">
-        <v>558</v>
-      </c>
-      <c r="H5" t="s">
-        <v>561</v>
-      </c>
-      <c r="J5" t="s">
-        <v>571</v>
-      </c>
-      <c r="P5" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>585</v>
-      </c>
-      <c r="B6" s="49" t="s">
-        <v>540</v>
-      </c>
-      <c r="D6" s="49" t="s">
-        <v>548</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>773</v>
-      </c>
-      <c r="H6" t="s">
-        <v>775</v>
-      </c>
-      <c r="J6" t="s">
-        <v>554</v>
-      </c>
-      <c r="P6" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>586</v>
-      </c>
-      <c r="B7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="H7" t="s">
-        <v>774</v>
-      </c>
-      <c r="J7" t="s">
-        <v>572</v>
-      </c>
-      <c r="P7" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>587</v>
-      </c>
-      <c r="B8" t="s">
-        <v>575</v>
-      </c>
-      <c r="D8" t="s">
-        <v>580</v>
-      </c>
-      <c r="F8" t="s">
-        <v>609</v>
-      </c>
-      <c r="H8" t="s">
-        <v>609</v>
-      </c>
-      <c r="J8" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>588</v>
-      </c>
-      <c r="B9" t="s">
-        <v>541</v>
-      </c>
-      <c r="D9" t="s">
-        <v>610</v>
-      </c>
-      <c r="F9" t="s">
-        <v>573</v>
-      </c>
-      <c r="H9" t="s">
-        <v>562</v>
-      </c>
-      <c r="J9" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>589</v>
-      </c>
-      <c r="B10" t="s">
-        <v>611</v>
-      </c>
-      <c r="D10" t="s">
-        <v>549</v>
-      </c>
-      <c r="F10" t="s">
-        <v>559</v>
-      </c>
-      <c r="H10" t="s">
-        <v>563</v>
-      </c>
-      <c r="J10" t="s">
-        <v>559</v>
-      </c>
-      <c r="P10" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>590</v>
-      </c>
-      <c r="B11" t="s">
-        <v>542</v>
-      </c>
-      <c r="D11" t="s">
-        <v>550</v>
-      </c>
-      <c r="F11" t="s">
-        <v>555</v>
-      </c>
-      <c r="H11" t="s">
-        <v>564</v>
-      </c>
-      <c r="J11" t="s">
-        <v>603</v>
-      </c>
-      <c r="P11" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>591</v>
-      </c>
-      <c r="B12" t="s">
-        <v>613</v>
-      </c>
-      <c r="D12" t="s">
-        <v>551</v>
-      </c>
-      <c r="F12" t="s">
-        <v>615</v>
-      </c>
-      <c r="H12" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>592</v>
-      </c>
-      <c r="B13" t="s">
-        <v>614</v>
-      </c>
-      <c r="D13" t="s">
-        <v>600</v>
-      </c>
-      <c r="F13" t="s">
-        <v>601</v>
-      </c>
-      <c r="H13" t="s">
-        <v>599</v>
-      </c>
-      <c r="J13" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>593</v>
-      </c>
-      <c r="B14" t="s">
-        <v>543</v>
-      </c>
-      <c r="D14" t="s">
-        <v>552</v>
-      </c>
-      <c r="H14" t="s">
-        <v>565</v>
-      </c>
-      <c r="P14" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>594</v>
-      </c>
-      <c r="B15" t="s">
-        <v>546</v>
-      </c>
-      <c r="H15" t="s">
-        <v>567</v>
-      </c>
-      <c r="J15" t="s">
-        <v>581</v>
-      </c>
-      <c r="P15" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>595</v>
-      </c>
-      <c r="B16" t="s">
-        <v>545</v>
-      </c>
-      <c r="F16" t="s">
-        <v>556</v>
-      </c>
-      <c r="H16" t="s">
-        <v>566</v>
-      </c>
-      <c r="P16" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>596</v>
-      </c>
-      <c r="B17" t="s">
-        <v>544</v>
-      </c>
-      <c r="D17" t="s">
-        <v>553</v>
-      </c>
-      <c r="F17" t="s">
-        <v>556</v>
-      </c>
-      <c r="H17" t="s">
-        <v>568</v>
-      </c>
-      <c r="P17" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>597</v>
-      </c>
-      <c r="B18" t="s">
-        <v>576</v>
-      </c>
-      <c r="D18" t="s">
-        <v>578</v>
-      </c>
-      <c r="F18" t="s">
-        <v>557</v>
-      </c>
-      <c r="H18" t="s">
-        <v>569</v>
-      </c>
-      <c r="J18" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>598</v>
-      </c>
-      <c r="B19" t="s">
-        <v>577</v>
-      </c>
-      <c r="D19" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P20" s="11" t="s">
-        <v>528</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B6:B7"/>
-  </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>